--- a/diseases/d064/2010-2014.xlsx
+++ b/diseases/d064/2010-2014.xlsx
@@ -1157,6 +1157,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1683,6 +1688,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1827,6 +1837,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1968,6 +1983,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2112,6 +2132,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2253,6 +2278,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2397,6 +2427,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2538,6 +2573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2682,6 +2722,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2823,6 +2868,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2967,6 +3017,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3108,6 +3163,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3252,6 +3312,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3393,6 +3458,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3537,6 +3607,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3678,6 +3753,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3822,6 +3902,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3963,6 +4048,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4107,6 +4197,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4248,6 +4343,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4392,6 +4492,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4533,6 +4638,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4677,6 +4787,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4818,6 +4933,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5347,6 +5467,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5873,6 +5998,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6017,6 +6147,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6158,6 +6293,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6302,6 +6442,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6443,6 +6588,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6587,6 +6737,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6728,6 +6883,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6872,6 +7032,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7013,6 +7178,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7157,6 +7327,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7298,6 +7473,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7442,6 +7622,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7583,6 +7768,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7727,6 +7917,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7868,6 +8063,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8012,6 +8212,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8153,6 +8358,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8297,6 +8507,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8438,6 +8653,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8582,6 +8802,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8723,6 +8948,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8867,6 +9097,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9008,6 +9243,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9537,6 +9777,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10063,6 +10308,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10207,6 +10457,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10348,6 +10603,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10492,6 +10752,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10633,6 +10898,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10777,6 +11047,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10918,6 +11193,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11062,6 +11342,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11203,6 +11488,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11347,6 +11637,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11488,6 +11783,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11632,6 +11932,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11773,6 +12078,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11917,6 +12227,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12058,6 +12373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12202,6 +12522,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12343,6 +12668,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12919,6 +13249,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13060,6 +13395,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13780,6 +14120,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13921,6 +14266,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14785,6 +15135,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14926,6 +15281,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16031,6 +16391,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16557,6 +16922,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17277,6 +17647,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17562,6 +17937,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18138,6 +18518,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18423,6 +18808,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19143,6 +19533,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19284,6 +19679,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20004,6 +20404,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20145,6 +20550,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21009,6 +21419,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21150,6 +21565,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21870,6 +22290,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22011,6 +22436,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22731,6 +23161,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22872,6 +23307,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23736,6 +24176,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23877,6 +24322,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24597,6 +25047,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24738,6 +25193,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25458,6 +25918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25743,6 +26208,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26463,6 +26933,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26604,6 +27079,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27709,6 +28189,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28235,6 +28720,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29099,6 +29589,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29240,6 +29735,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29960,6 +30460,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30101,6 +30606,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30821,6 +31331,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30962,6 +31477,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31682,6 +32202,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31823,6 +32348,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32687,6 +33217,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32828,6 +33363,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33548,6 +34088,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33689,6 +34234,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34409,6 +34959,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34694,6 +35249,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35414,6 +35974,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35555,6 +36120,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36275,6 +36845,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36416,6 +36991,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37280,6 +37860,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37421,6 +38006,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38141,6 +38731,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38280,6 +38875,11 @@
       <c r="S257" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO257" t="inlineStr">

--- a/diseases/d064/2010-2014.xlsx
+++ b/diseases/d064/2010-2014.xlsx
@@ -12817,28 +12817,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -12961,28 +12975,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -13105,28 +13133,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -13544,28 +13586,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -13688,28 +13744,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -13832,28 +13902,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -13976,28 +14060,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -14415,28 +14513,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
@@ -14559,28 +14671,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
@@ -14703,28 +14829,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
@@ -14847,28 +14987,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
@@ -14991,28 +15145,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -15430,28 +15598,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
@@ -15574,28 +15756,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -15718,28 +15914,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
@@ -15862,28 +16072,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
@@ -17071,28 +17295,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -17215,28 +17453,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -17359,28 +17611,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -17503,28 +17769,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -17796,28 +18076,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
@@ -18086,28 +18380,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -18230,28 +18538,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -18374,28 +18696,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
@@ -18667,28 +19003,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
@@ -18957,28 +19307,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -19101,28 +19465,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
@@ -19245,28 +19623,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
@@ -19389,28 +19781,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
@@ -19828,28 +20234,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
@@ -19972,28 +20392,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
@@ -20116,28 +20550,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
@@ -20260,28 +20708,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -20699,28 +21161,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
@@ -20843,28 +21319,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
@@ -20987,28 +21477,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
@@ -21131,28 +21635,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
@@ -21275,28 +21793,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -21714,28 +22246,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
@@ -21858,28 +22404,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
@@ -22002,28 +22562,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
@@ -22146,28 +22720,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
@@ -22585,28 +23173,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
@@ -22729,28 +23331,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
@@ -22873,28 +23489,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS148" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
@@ -23017,28 +23647,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
@@ -23456,28 +24100,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
@@ -23600,28 +24258,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS153" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
@@ -23744,28 +24416,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS154" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
@@ -23888,28 +24574,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
@@ -24032,28 +24732,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
@@ -24471,28 +25185,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
@@ -24615,28 +25343,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
@@ -24759,28 +25501,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
@@ -24903,28 +25659,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
@@ -25342,28 +26112,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
@@ -25486,28 +26270,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
@@ -25630,28 +26428,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
@@ -25774,28 +26586,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
@@ -26067,28 +26893,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
@@ -26357,28 +27197,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS172" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
@@ -26501,28 +27355,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
@@ -26645,28 +27513,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
@@ -26789,28 +27671,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
@@ -27228,28 +28124,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS178" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ178" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
@@ -27372,28 +28282,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS179" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
@@ -27516,28 +28440,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR180" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ180" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
@@ -27660,28 +28598,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR181" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS181" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ181" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
@@ -28869,28 +29821,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR188" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS188" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ188" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
@@ -29013,28 +29979,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR189" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
@@ -29157,28 +30137,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
@@ -29301,28 +30295,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR191" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
@@ -29445,28 +30453,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS192" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ192" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
@@ -29884,28 +30906,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
@@ -30028,28 +31064,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
@@ -30172,28 +31222,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
@@ -30316,28 +31380,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR198" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
@@ -30755,28 +31833,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
@@ -30899,28 +31991,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR202" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS202" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
@@ -31043,28 +32149,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
@@ -31187,28 +32307,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
@@ -31626,28 +32760,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
@@ -31770,28 +32918,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR208" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
@@ -31914,28 +33076,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR209" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
@@ -32058,28 +33234,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
@@ -32497,28 +33687,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR213" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
@@ -32641,28 +33845,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR214" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS214" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ214" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
@@ -32785,28 +34003,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR215" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
@@ -32929,28 +34161,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR216" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS216" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ216" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
@@ -33073,28 +34319,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS217" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
@@ -33512,28 +34772,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR220" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ220" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
@@ -33656,28 +34930,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR221" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS221" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
@@ -33800,28 +35088,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR222" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS222" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ222" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
@@ -33944,28 +35246,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS223" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ223" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
@@ -34383,28 +35699,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR226" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
@@ -34527,28 +35857,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR227" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS227" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ227" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
@@ -34671,28 +36015,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR228" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
@@ -34815,28 +36173,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR229" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS229" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ229" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
@@ -35108,28 +36480,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR231" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ231" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
@@ -35398,28 +36784,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR233" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
@@ -35542,28 +36942,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR234" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
@@ -35686,28 +37100,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR235" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ235" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
@@ -35830,28 +37258,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR236" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ236" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
@@ -36269,28 +37711,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR239" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ239" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
@@ -36413,28 +37869,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR240" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ240" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
@@ -36557,28 +38027,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR241" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS241" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ241" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
@@ -36701,28 +38185,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR242" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ242" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
@@ -37140,28 +38638,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR245" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS245" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ245" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
@@ -37284,28 +38796,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR246" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS246" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ246" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
@@ -37428,28 +38954,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR247" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS247" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ247" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
@@ -37572,28 +39112,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR248" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
@@ -37716,28 +39270,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR249" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS249" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ249" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
@@ -38155,28 +39723,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
@@ -38299,28 +39881,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR253" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS253" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ253" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
@@ -38443,28 +40039,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR254" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
@@ -38587,28 +40197,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR255" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS255" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ255" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
@@ -39026,28 +40650,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR258" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS258" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ258" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
@@ -39170,28 +40808,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR259" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS259" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ259" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
@@ -39314,28 +40966,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR260" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS260" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ260" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
@@ -39458,28 +41124,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR261" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS261" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ261" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr">
+        <is>
+          <t>HOLD_JP_d38d722b1e545df114640333e053</t>
+        </is>
+      </c>
       <c r="AT261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">

--- a/diseases/d064/2010-2014.xlsx
+++ b/diseases/d064/2010-2014.xlsx
@@ -11081,17 +11081,15 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U77" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -11099,7 +11097,7 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -11109,12 +11107,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
@@ -11124,11 +11117,6 @@
       </c>
       <c r="AT77" t="n">
         <v>1</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -11239,17 +11227,15 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U78" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -11257,7 +11243,7 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -11267,12 +11253,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ78" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
@@ -11282,11 +11263,6 @@
       </c>
       <c r="AT78" t="n">
         <v>1</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -11397,17 +11373,15 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U79" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -11415,7 +11389,7 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -11425,12 +11399,7 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ79" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
@@ -11440,11 +11409,6 @@
       </c>
       <c r="AT79" t="n">
         <v>1</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -11820,17 +11784,15 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U82" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -11838,7 +11800,7 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -11848,12 +11810,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
@@ -11863,11 +11820,6 @@
       </c>
       <c r="AT82" t="n">
         <v>1</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -11978,17 +11930,15 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U83" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -11996,7 +11946,7 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -12006,12 +11956,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ83" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
@@ -12021,11 +11966,6 @@
       </c>
       <c r="AT83" t="n">
         <v>1</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -12136,17 +12076,15 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U84" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -12154,7 +12092,7 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -12164,12 +12102,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ84" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
@@ -12179,11 +12112,6 @@
       </c>
       <c r="AT84" t="n">
         <v>1</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -12294,17 +12222,15 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U85" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -12312,7 +12238,7 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -12322,12 +12248,7 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ85" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr">
@@ -12337,11 +12258,6 @@
       </c>
       <c r="AT85" t="n">
         <v>1</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -12717,17 +12633,15 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U88" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -12735,7 +12649,7 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -12745,12 +12659,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ88" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
@@ -12760,11 +12669,6 @@
       </c>
       <c r="AT88" t="n">
         <v>1</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -12875,17 +12779,15 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U89" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -12893,7 +12795,7 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -12903,12 +12805,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
@@ -12918,11 +12815,6 @@
       </c>
       <c r="AT89" t="n">
         <v>1</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -13033,17 +12925,15 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U90" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -13051,7 +12941,7 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -13061,12 +12951,7 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
@@ -13076,11 +12961,6 @@
       </c>
       <c r="AT90" t="n">
         <v>1</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -13191,17 +13071,15 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U91" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -13209,7 +13087,7 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -13219,12 +13097,7 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ91" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
@@ -13234,11 +13107,6 @@
       </c>
       <c r="AT91" t="n">
         <v>1</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -13349,17 +13217,15 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U92" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -13367,7 +13233,7 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -13377,12 +13243,7 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ92" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr">
@@ -13392,11 +13253,6 @@
       </c>
       <c r="AT92" t="n">
         <v>1</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -13772,17 +13628,15 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U95" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -13790,7 +13644,7 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -13800,12 +13654,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
@@ -13815,11 +13664,6 @@
       </c>
       <c r="AT95" t="n">
         <v>1</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -13930,17 +13774,15 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U96" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -13948,7 +13790,7 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -13958,12 +13800,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ96" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
@@ -13973,11 +13810,6 @@
       </c>
       <c r="AT96" t="n">
         <v>1</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -14088,17 +13920,15 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U97" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -14106,7 +13936,7 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -14116,12 +13946,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ97" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
@@ -14131,11 +13956,6 @@
       </c>
       <c r="AT97" t="n">
         <v>1</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -14246,17 +14066,15 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U98" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -14264,7 +14082,7 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -14274,12 +14092,7 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ98" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
@@ -14289,11 +14102,6 @@
       </c>
       <c r="AT98" t="n">
         <v>1</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -15194,17 +15002,15 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
       <c r="Q104" t="n">
         <v>0</v>
       </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U104" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -15212,7 +15018,7 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -15222,12 +15028,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
@@ -15237,11 +15038,6 @@
       </c>
       <c r="AT104" t="n">
         <v>1</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -15352,17 +15148,15 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
       <c r="Q105" t="n">
         <v>0</v>
       </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U105" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -15370,7 +15164,7 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -15380,12 +15174,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ105" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
@@ -15395,11 +15184,6 @@
       </c>
       <c r="AT105" t="n">
         <v>1</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -15510,17 +15294,15 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U106" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -15528,7 +15310,7 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -15538,12 +15320,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ106" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
@@ -15553,11 +15330,6 @@
       </c>
       <c r="AT106" t="n">
         <v>1</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -15668,17 +15440,15 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U107" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -15686,7 +15456,7 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -15696,12 +15466,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
@@ -15711,11 +15476,6 @@
       </c>
       <c r="AT107" t="n">
         <v>1</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -15960,17 +15720,15 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U109" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -15978,7 +15736,7 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -15988,12 +15746,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
@@ -16003,11 +15756,6 @@
       </c>
       <c r="AT109" t="n">
         <v>1</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -16249,17 +15997,15 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U111" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -16267,7 +16013,7 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -16277,12 +16023,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
@@ -16292,11 +16033,6 @@
       </c>
       <c r="AT111" t="n">
         <v>1</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -16407,17 +16143,15 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U112" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -16425,7 +16159,7 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -16435,12 +16169,7 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
@@ -16450,11 +16179,6 @@
       </c>
       <c r="AT112" t="n">
         <v>1</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -16565,17 +16289,15 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U113" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -16583,7 +16305,7 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -16593,12 +16315,7 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ113" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
@@ -16608,11 +16325,6 @@
       </c>
       <c r="AT113" t="n">
         <v>1</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -16857,17 +16569,15 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U115" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -16875,7 +16585,7 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -16885,12 +16595,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
@@ -16900,11 +16605,6 @@
       </c>
       <c r="AT115" t="n">
         <v>1</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -17146,17 +16846,15 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U117" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -17164,7 +16862,7 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -17174,12 +16872,7 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ117" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
@@ -17189,11 +16882,6 @@
       </c>
       <c r="AT117" t="n">
         <v>1</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -17304,17 +16992,15 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U118" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -17322,7 +17008,7 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -17332,12 +17018,7 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
@@ -17347,11 +17028,6 @@
       </c>
       <c r="AT118" t="n">
         <v>1</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -17462,17 +17138,15 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U119" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -17480,7 +17154,7 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -17490,12 +17164,7 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
@@ -17505,11 +17174,6 @@
       </c>
       <c r="AT119" t="n">
         <v>1</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -17620,17 +17284,15 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -17638,7 +17300,7 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -17648,12 +17310,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
@@ -17663,11 +17320,6 @@
       </c>
       <c r="AT120" t="n">
         <v>1</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -18043,17 +17695,15 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U123" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -18061,7 +17711,7 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -18071,12 +17721,7 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr">
@@ -18086,11 +17731,6 @@
       </c>
       <c r="AT123" t="n">
         <v>1</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -18201,17 +17841,15 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
       <c r="Q124" t="n">
         <v>0</v>
       </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U124" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -18219,7 +17857,7 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -18229,12 +17867,7 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr">
@@ -18244,11 +17877,6 @@
       </c>
       <c r="AT124" t="n">
         <v>1</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -18359,17 +17987,15 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
       <c r="Q125" t="n">
         <v>0</v>
       </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U125" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -18377,7 +18003,7 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -18387,12 +18013,7 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
@@ -18402,11 +18023,6 @@
       </c>
       <c r="AT125" t="n">
         <v>1</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -18517,17 +18133,15 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
       <c r="Q126" t="n">
         <v>0</v>
       </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U126" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -18535,7 +18149,7 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -18545,12 +18159,7 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
@@ -18560,11 +18169,6 @@
       </c>
       <c r="AT126" t="n">
         <v>1</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -18940,17 +18544,15 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
       <c r="Q129" t="n">
         <v>0</v>
       </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U129" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -18958,7 +18560,7 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -18968,12 +18570,7 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ129" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
@@ -18983,11 +18580,6 @@
       </c>
       <c r="AT129" t="n">
         <v>1</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -19098,17 +18690,15 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U130" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -19116,7 +18706,7 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -19126,12 +18716,7 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ130" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
@@ -19141,11 +18726,6 @@
       </c>
       <c r="AT130" t="n">
         <v>1</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -19256,17 +18836,15 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U131" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -19274,7 +18852,7 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -19284,12 +18862,7 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
@@ -19299,11 +18872,6 @@
       </c>
       <c r="AT131" t="n">
         <v>1</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -19414,17 +18982,15 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
       <c r="Q132" t="n">
         <v>0</v>
       </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U132" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -19432,7 +18998,7 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -19442,12 +19008,7 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ132" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
@@ -19457,11 +19018,6 @@
       </c>
       <c r="AT132" t="n">
         <v>1</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -19572,17 +19128,15 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U133" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -19590,7 +19144,7 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -19600,12 +19154,7 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ133" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
@@ -19615,11 +19164,6 @@
       </c>
       <c r="AT133" t="n">
         <v>1</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -19995,17 +19539,15 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
       <c r="Q136" t="n">
         <v>0</v>
       </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U136" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -20013,7 +19555,7 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -20023,12 +19565,7 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
@@ -20038,11 +19575,6 @@
       </c>
       <c r="AT136" t="n">
         <v>1</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -20153,17 +19685,15 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U137" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -20171,7 +19701,7 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -20181,12 +19711,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
@@ -20196,11 +19721,6 @@
       </c>
       <c r="AT137" t="n">
         <v>1</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -20311,17 +19831,15 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U138" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -20329,7 +19847,7 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -20339,12 +19857,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ138" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr">
@@ -20354,11 +19867,6 @@
       </c>
       <c r="AT138" t="n">
         <v>1</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -20469,17 +19977,15 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
       <c r="Q139" t="n">
         <v>0</v>
       </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U139" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -20487,7 +19993,7 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -20497,12 +20003,7 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ139" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr">
@@ -20512,11 +20013,6 @@
       </c>
       <c r="AT139" t="n">
         <v>1</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -20892,17 +20388,15 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
       <c r="Q142" t="n">
         <v>0</v>
       </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U142" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -20910,7 +20404,7 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -20920,12 +20414,7 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ142" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
@@ -20935,11 +20424,6 @@
       </c>
       <c r="AT142" t="n">
         <v>1</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -21050,17 +20534,15 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
       <c r="Q143" t="n">
         <v>0</v>
       </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U143" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -21068,7 +20550,7 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -21078,12 +20560,7 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr">
@@ -21093,11 +20570,6 @@
       </c>
       <c r="AT143" t="n">
         <v>1</v>
-      </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -21208,17 +20680,15 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
       <c r="Q144" t="n">
         <v>0</v>
       </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U144" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -21226,7 +20696,7 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -21236,12 +20706,7 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ144" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr">
@@ -21251,11 +20716,6 @@
       </c>
       <c r="AT144" t="n">
         <v>1</v>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -21366,17 +20826,15 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
       <c r="Q145" t="n">
         <v>0</v>
       </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U145" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -21384,7 +20842,7 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
@@ -21394,12 +20852,7 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ145" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
@@ -21409,11 +20862,6 @@
       </c>
       <c r="AT145" t="n">
         <v>1</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -21789,17 +21237,15 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
       <c r="Q148" t="n">
         <v>0</v>
       </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U148" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -21807,7 +21253,7 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -21817,12 +21263,7 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ148" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr">
@@ -21832,11 +21273,6 @@
       </c>
       <c r="AT148" t="n">
         <v>1</v>
-      </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -21947,17 +21383,15 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
       <c r="Q149" t="n">
         <v>0</v>
       </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U149" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -21965,7 +21399,7 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -21975,12 +21409,7 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ149" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr">
@@ -21990,11 +21419,6 @@
       </c>
       <c r="AT149" t="n">
         <v>1</v>
-      </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -22105,17 +21529,15 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
       <c r="Q150" t="n">
         <v>0</v>
       </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U150" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -22123,7 +21545,7 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -22133,12 +21555,7 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ150" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
@@ -22148,11 +21565,6 @@
       </c>
       <c r="AT150" t="n">
         <v>1</v>
-      </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -22263,17 +21675,15 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
       <c r="Q151" t="n">
         <v>0</v>
       </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U151" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -22281,7 +21691,7 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -22291,12 +21701,7 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ151" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
@@ -22306,11 +21711,6 @@
       </c>
       <c r="AT151" t="n">
         <v>1</v>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -22421,17 +21821,15 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
       <c r="Q152" t="n">
         <v>0</v>
       </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U152" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -22439,7 +21837,7 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -22449,12 +21847,7 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ152" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
@@ -22464,11 +21857,6 @@
       </c>
       <c r="AT152" t="n">
         <v>1</v>
-      </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
@@ -22844,17 +22232,15 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
       <c r="Q155" t="n">
         <v>0</v>
       </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U155" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -22862,7 +22248,7 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -22872,12 +22258,7 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ155" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
@@ -22887,11 +22268,6 @@
       </c>
       <c r="AT155" t="n">
         <v>1</v>
-      </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -23002,17 +22378,15 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
       <c r="Q156" t="n">
         <v>0</v>
       </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U156" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -23020,7 +22394,7 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -23030,12 +22404,7 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ156" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
@@ -23045,11 +22414,6 @@
       </c>
       <c r="AT156" t="n">
         <v>1</v>
-      </c>
-      <c r="AU156" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -23160,17 +22524,15 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
       <c r="Q157" t="n">
         <v>0</v>
       </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U157" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -23178,7 +22540,7 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -23188,12 +22550,7 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ157" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr">
@@ -23203,11 +22560,6 @@
       </c>
       <c r="AT157" t="n">
         <v>1</v>
-      </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -23318,17 +22670,15 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
       <c r="Q158" t="n">
         <v>0</v>
       </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U158" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -23336,7 +22686,7 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -23346,12 +22696,7 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ158" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr">
@@ -23361,11 +22706,6 @@
       </c>
       <c r="AT158" t="n">
         <v>1</v>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -23741,17 +23081,15 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
       <c r="Q161" t="n">
         <v>0</v>
       </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U161" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -23759,7 +23097,7 @@
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -23769,12 +23107,7 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ161" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr">
@@ -23784,11 +23117,6 @@
       </c>
       <c r="AT161" t="n">
         <v>1</v>
-      </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -23899,17 +23227,15 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
       <c r="Q162" t="n">
         <v>0</v>
       </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U162" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -23917,7 +23243,7 @@
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -23927,12 +23253,7 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
@@ -23942,11 +23263,6 @@
       </c>
       <c r="AT162" t="n">
         <v>1</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -24057,17 +23373,15 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
       <c r="Q163" t="n">
         <v>0</v>
       </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U163" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -24075,7 +23389,7 @@
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
@@ -24085,12 +23399,7 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr">
@@ -24100,11 +23409,6 @@
       </c>
       <c r="AT163" t="n">
         <v>1</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
@@ -24215,17 +23519,15 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
       <c r="Q164" t="n">
         <v>0</v>
       </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U164" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -24233,7 +23535,7 @@
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -24243,12 +23545,7 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ164" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr">
@@ -24258,11 +23555,6 @@
       </c>
       <c r="AT164" t="n">
         <v>1</v>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -24507,17 +23799,15 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
       <c r="Q166" t="n">
         <v>0</v>
       </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U166" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -24525,7 +23815,7 @@
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
@@ -24535,12 +23825,7 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ166" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr">
@@ -24550,11 +23835,6 @@
       </c>
       <c r="AT166" t="n">
         <v>1</v>
-      </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
@@ -24796,17 +24076,15 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
       <c r="Q168" t="n">
         <v>0</v>
       </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U168" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -24814,7 +24092,7 @@
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
@@ -24824,12 +24102,7 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ168" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr">
@@ -24839,11 +24112,6 @@
       </c>
       <c r="AT168" t="n">
         <v>1</v>
-      </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
@@ -24954,17 +24222,15 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
       <c r="Q169" t="n">
         <v>0</v>
       </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U169" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -24972,7 +24238,7 @@
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -24982,12 +24248,7 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ169" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr">
@@ -24997,11 +24258,6 @@
       </c>
       <c r="AT169" t="n">
         <v>1</v>
-      </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -25112,17 +24368,15 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
       <c r="Q170" t="n">
         <v>0</v>
       </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U170" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -25130,7 +24384,7 @@
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -25140,12 +24394,7 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ170" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr">
@@ -25155,11 +24404,6 @@
       </c>
       <c r="AT170" t="n">
         <v>1</v>
-      </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -25270,17 +24514,15 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
       <c r="Q171" t="n">
         <v>0</v>
       </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U171" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -25288,7 +24530,7 @@
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -25298,12 +24540,7 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ171" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr">
@@ -25313,11 +24550,6 @@
       </c>
       <c r="AT171" t="n">
         <v>1</v>
-      </c>
-      <c r="AU171" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -25693,17 +24925,15 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
+      <c r="P174" t="n">
+        <v>0</v>
+      </c>
       <c r="Q174" t="n">
         <v>0</v>
       </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U174" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -25711,7 +24941,7 @@
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -25721,12 +24951,7 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ174" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr">
@@ -25736,11 +24961,6 @@
       </c>
       <c r="AT174" t="n">
         <v>1</v>
-      </c>
-      <c r="AU174" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
@@ -25851,17 +25071,15 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
+      <c r="P175" t="n">
+        <v>0</v>
+      </c>
       <c r="Q175" t="n">
         <v>0</v>
       </c>
       <c r="R175" t="n">
         <v>0</v>
       </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U175" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -25869,7 +25087,7 @@
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -25879,12 +25097,7 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ175" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr">
@@ -25894,11 +25107,6 @@
       </c>
       <c r="AT175" t="n">
         <v>1</v>
-      </c>
-      <c r="AU175" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
@@ -26009,17 +25217,15 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
+      <c r="P176" t="n">
+        <v>0</v>
+      </c>
       <c r="Q176" t="n">
         <v>0</v>
       </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U176" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -26027,7 +25233,7 @@
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -26037,12 +25243,7 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ176" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr">
@@ -26052,11 +25253,6 @@
       </c>
       <c r="AT176" t="n">
         <v>1</v>
-      </c>
-      <c r="AU176" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
@@ -26167,17 +25363,15 @@
       <c r="O177" t="n">
         <v>0</v>
       </c>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
       <c r="Q177" t="n">
         <v>0</v>
       </c>
       <c r="R177" t="n">
         <v>0</v>
       </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U177" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -26185,7 +25379,7 @@
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
@@ -26195,12 +25389,7 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ177" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr">
@@ -26210,11 +25399,6 @@
       </c>
       <c r="AT177" t="n">
         <v>1</v>
-      </c>
-      <c r="AU177" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
@@ -27115,17 +26299,15 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
       <c r="Q183" t="n">
         <v>0</v>
       </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U183" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -27133,7 +26315,7 @@
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
@@ -27143,12 +26325,7 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ183" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr">
@@ -27158,11 +26335,6 @@
       </c>
       <c r="AT183" t="n">
         <v>1</v>
-      </c>
-      <c r="AU183" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
@@ -27273,17 +26445,15 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
+      <c r="P184" t="n">
+        <v>0</v>
+      </c>
       <c r="Q184" t="n">
         <v>0</v>
       </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U184" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -27291,7 +26461,7 @@
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
@@ -27301,12 +26471,7 @@
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ184" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr">
@@ -27316,11 +26481,6 @@
       </c>
       <c r="AT184" t="n">
         <v>1</v>
-      </c>
-      <c r="AU184" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
@@ -27431,17 +26591,15 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
+      <c r="P185" t="n">
+        <v>0</v>
+      </c>
       <c r="Q185" t="n">
         <v>0</v>
       </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U185" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -27449,7 +26607,7 @@
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
@@ -27459,12 +26617,7 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ185" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr">
@@ -27474,11 +26627,6 @@
       </c>
       <c r="AT185" t="n">
         <v>1</v>
-      </c>
-      <c r="AU185" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
@@ -27589,17 +26737,15 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
+      <c r="P186" t="n">
+        <v>0</v>
+      </c>
       <c r="Q186" t="n">
         <v>0</v>
       </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U186" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -27607,7 +26753,7 @@
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
@@ -27617,12 +26763,7 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ186" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr">
@@ -27632,11 +26773,6 @@
       </c>
       <c r="AT186" t="n">
         <v>1</v>
-      </c>
-      <c r="AU186" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
@@ -27747,17 +26883,15 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
       <c r="Q187" t="n">
         <v>0</v>
       </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U187" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -27765,7 +26899,7 @@
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
@@ -27775,12 +26909,7 @@
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ187" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr">
@@ -27790,11 +26919,6 @@
       </c>
       <c r="AT187" t="n">
         <v>1</v>
-      </c>
-      <c r="AU187" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
@@ -28170,17 +27294,15 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
+      <c r="P190" t="n">
+        <v>0</v>
+      </c>
       <c r="Q190" t="n">
         <v>0</v>
       </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U190" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -28188,7 +27310,7 @@
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
@@ -28198,12 +27320,7 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ190" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr">
@@ -28213,11 +27330,6 @@
       </c>
       <c r="AT190" t="n">
         <v>1</v>
-      </c>
-      <c r="AU190" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
@@ -28328,17 +27440,15 @@
       <c r="O191" t="n">
         <v>0</v>
       </c>
+      <c r="P191" t="n">
+        <v>0</v>
+      </c>
       <c r="Q191" t="n">
         <v>0</v>
       </c>
       <c r="R191" t="n">
         <v>0</v>
       </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U191" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -28346,7 +27456,7 @@
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO191" t="inlineStr">
@@ -28356,12 +27466,7 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ191" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr">
@@ -28371,11 +27476,6 @@
       </c>
       <c r="AT191" t="n">
         <v>1</v>
-      </c>
-      <c r="AU191" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
@@ -28486,17 +27586,15 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
+      <c r="P192" t="n">
+        <v>0</v>
+      </c>
       <c r="Q192" t="n">
         <v>0</v>
       </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U192" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -28504,7 +27602,7 @@
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
@@ -28514,12 +27612,7 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ192" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr">
@@ -28529,11 +27622,6 @@
       </c>
       <c r="AT192" t="n">
         <v>1</v>
-      </c>
-      <c r="AU192" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
@@ -28644,17 +27732,15 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
+      <c r="P193" t="n">
+        <v>0</v>
+      </c>
       <c r="Q193" t="n">
         <v>0</v>
       </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U193" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -28662,7 +27748,7 @@
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO193" t="inlineStr">
@@ -28672,12 +27758,7 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ193" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr">
@@ -28687,11 +27768,6 @@
       </c>
       <c r="AT193" t="n">
         <v>1</v>
-      </c>
-      <c r="AU193" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
@@ -29067,17 +28143,15 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
+      <c r="P196" t="n">
+        <v>0</v>
+      </c>
       <c r="Q196" t="n">
         <v>0</v>
       </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U196" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -29085,7 +28159,7 @@
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO196" t="inlineStr">
@@ -29095,12 +28169,7 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ196" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS196" t="inlineStr">
@@ -29110,11 +28179,6 @@
       </c>
       <c r="AT196" t="n">
         <v>1</v>
-      </c>
-      <c r="AU196" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
@@ -29225,17 +28289,15 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
+      <c r="P197" t="n">
+        <v>0</v>
+      </c>
       <c r="Q197" t="n">
         <v>0</v>
       </c>
       <c r="R197" t="n">
         <v>0</v>
       </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U197" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -29243,7 +28305,7 @@
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
@@ -29253,12 +28315,7 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ197" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS197" t="inlineStr">
@@ -29268,11 +28325,6 @@
       </c>
       <c r="AT197" t="n">
         <v>1</v>
-      </c>
-      <c r="AU197" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
@@ -29383,17 +28435,15 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
       <c r="Q198" t="n">
         <v>0</v>
       </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U198" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -29401,7 +28451,7 @@
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
@@ -29411,12 +28461,7 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ198" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr">
@@ -29426,11 +28471,6 @@
       </c>
       <c r="AT198" t="n">
         <v>1</v>
-      </c>
-      <c r="AU198" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
@@ -29541,17 +28581,15 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
+      <c r="P199" t="n">
+        <v>0</v>
+      </c>
       <c r="Q199" t="n">
         <v>0</v>
       </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U199" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -29559,7 +28597,7 @@
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
@@ -29569,12 +28607,7 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ199" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr">
@@ -29584,11 +28617,6 @@
       </c>
       <c r="AT199" t="n">
         <v>1</v>
-      </c>
-      <c r="AU199" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
@@ -29964,17 +28992,15 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
+      <c r="P202" t="n">
+        <v>0</v>
+      </c>
       <c r="Q202" t="n">
         <v>0</v>
       </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U202" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -29982,7 +29008,7 @@
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
@@ -29992,12 +29018,7 @@
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ202" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS202" t="inlineStr">
@@ -30007,11 +29028,6 @@
       </c>
       <c r="AT202" t="n">
         <v>1</v>
-      </c>
-      <c r="AU202" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
@@ -30122,17 +29138,15 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
+      <c r="P203" t="n">
+        <v>0</v>
+      </c>
       <c r="Q203" t="n">
         <v>0</v>
       </c>
       <c r="R203" t="n">
         <v>0</v>
       </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U203" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -30140,7 +29154,7 @@
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO203" t="inlineStr">
@@ -30150,12 +29164,7 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ203" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS203" t="inlineStr">
@@ -30165,11 +29174,6 @@
       </c>
       <c r="AT203" t="n">
         <v>1</v>
-      </c>
-      <c r="AU203" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
@@ -30280,17 +29284,15 @@
       <c r="O204" t="n">
         <v>0</v>
       </c>
+      <c r="P204" t="n">
+        <v>0</v>
+      </c>
       <c r="Q204" t="n">
         <v>0</v>
       </c>
       <c r="R204" t="n">
         <v>0</v>
       </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U204" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -30298,7 +29300,7 @@
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
@@ -30308,12 +29310,7 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr">
@@ -30323,11 +29320,6 @@
       </c>
       <c r="AT204" t="n">
         <v>1</v>
-      </c>
-      <c r="AU204" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
@@ -30438,17 +29430,15 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
+      <c r="P205" t="n">
+        <v>0</v>
+      </c>
       <c r="Q205" t="n">
         <v>0</v>
       </c>
       <c r="R205" t="n">
         <v>0</v>
       </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U205" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -30456,7 +29446,7 @@
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO205" t="inlineStr">
@@ -30466,12 +29456,7 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ205" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS205" t="inlineStr">
@@ -30481,11 +29466,6 @@
       </c>
       <c r="AT205" t="n">
         <v>1</v>
-      </c>
-      <c r="AU205" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
@@ -30861,17 +29841,15 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
+      <c r="P208" t="n">
+        <v>0</v>
+      </c>
       <c r="Q208" t="n">
         <v>0</v>
       </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
-      <c r="S208" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U208" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -30879,7 +29857,7 @@
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
@@ -30889,12 +29867,7 @@
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ208" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr">
@@ -30904,11 +29877,6 @@
       </c>
       <c r="AT208" t="n">
         <v>1</v>
-      </c>
-      <c r="AU208" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
@@ -31019,17 +29987,15 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
+      <c r="P209" t="n">
+        <v>0</v>
+      </c>
       <c r="Q209" t="n">
         <v>0</v>
       </c>
       <c r="R209" t="n">
         <v>0</v>
       </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U209" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -31037,7 +30003,7 @@
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO209" t="inlineStr">
@@ -31047,12 +30013,7 @@
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ209" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr">
@@ -31062,11 +30023,6 @@
       </c>
       <c r="AT209" t="n">
         <v>1</v>
-      </c>
-      <c r="AU209" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
@@ -31177,17 +30133,15 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
       <c r="Q210" t="n">
         <v>0</v>
       </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U210" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -31195,7 +30149,7 @@
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO210" t="inlineStr">
@@ -31205,12 +30159,7 @@
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ210" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr">
@@ -31220,11 +30169,6 @@
       </c>
       <c r="AT210" t="n">
         <v>1</v>
-      </c>
-      <c r="AU210" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
@@ -31335,17 +30279,15 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
       <c r="Q211" t="n">
         <v>0</v>
       </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U211" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -31353,7 +30295,7 @@
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
@@ -31363,12 +30305,7 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ211" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr">
@@ -31378,11 +30315,6 @@
       </c>
       <c r="AT211" t="n">
         <v>1</v>
-      </c>
-      <c r="AU211" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
@@ -31493,17 +30425,15 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
+      <c r="P212" t="n">
+        <v>0</v>
+      </c>
       <c r="Q212" t="n">
         <v>0</v>
       </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U212" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -31511,7 +30441,7 @@
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO212" t="inlineStr">
@@ -31521,12 +30451,7 @@
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ212" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr">
@@ -31536,11 +30461,6 @@
       </c>
       <c r="AT212" t="n">
         <v>1</v>
-      </c>
-      <c r="AU212" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
@@ -31916,17 +30836,15 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
       <c r="Q215" t="n">
         <v>0</v>
       </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U215" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -31934,7 +30852,7 @@
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO215" t="inlineStr">
@@ -31944,12 +30862,7 @@
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ215" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS215" t="inlineStr">
@@ -31959,11 +30872,6 @@
       </c>
       <c r="AT215" t="n">
         <v>1</v>
-      </c>
-      <c r="AU215" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
@@ -32074,17 +30982,15 @@
       <c r="O216" t="n">
         <v>0</v>
       </c>
+      <c r="P216" t="n">
+        <v>0</v>
+      </c>
       <c r="Q216" t="n">
         <v>0</v>
       </c>
       <c r="R216" t="n">
         <v>0</v>
       </c>
-      <c r="S216" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U216" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -32092,7 +30998,7 @@
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO216" t="inlineStr">
@@ -32102,12 +31008,7 @@
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ216" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS216" t="inlineStr">
@@ -32117,11 +31018,6 @@
       </c>
       <c r="AT216" t="n">
         <v>1</v>
-      </c>
-      <c r="AU216" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
@@ -32232,17 +31128,15 @@
       <c r="O217" t="n">
         <v>0</v>
       </c>
+      <c r="P217" t="n">
+        <v>0</v>
+      </c>
       <c r="Q217" t="n">
         <v>0</v>
       </c>
       <c r="R217" t="n">
         <v>0</v>
       </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U217" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -32250,7 +31144,7 @@
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
@@ -32260,12 +31154,7 @@
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ217" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS217" t="inlineStr">
@@ -32275,11 +31164,6 @@
       </c>
       <c r="AT217" t="n">
         <v>1</v>
-      </c>
-      <c r="AU217" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
@@ -32390,17 +31274,15 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
+      <c r="P218" t="n">
+        <v>0</v>
+      </c>
       <c r="Q218" t="n">
         <v>0</v>
       </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U218" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -32408,7 +31290,7 @@
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
@@ -32418,12 +31300,7 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ218" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr">
@@ -32433,11 +31310,6 @@
       </c>
       <c r="AT218" t="n">
         <v>1</v>
-      </c>
-      <c r="AU218" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
@@ -32813,17 +31685,15 @@
       <c r="O221" t="n">
         <v>0</v>
       </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
       <c r="Q221" t="n">
         <v>0</v>
       </c>
       <c r="R221" t="n">
         <v>0</v>
       </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U221" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -32831,7 +31701,7 @@
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO221" t="inlineStr">
@@ -32841,12 +31711,7 @@
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ221" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS221" t="inlineStr">
@@ -32856,11 +31721,6 @@
       </c>
       <c r="AT221" t="n">
         <v>1</v>
-      </c>
-      <c r="AU221" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
@@ -32971,17 +31831,15 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
+      <c r="P222" t="n">
+        <v>0</v>
+      </c>
       <c r="Q222" t="n">
         <v>0</v>
       </c>
       <c r="R222" t="n">
         <v>0</v>
       </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U222" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -32989,7 +31847,7 @@
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO222" t="inlineStr">
@@ -32999,12 +31857,7 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ222" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr">
@@ -33014,11 +31867,6 @@
       </c>
       <c r="AT222" t="n">
         <v>1</v>
-      </c>
-      <c r="AU222" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
@@ -33129,17 +31977,15 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
+      <c r="P223" t="n">
+        <v>0</v>
+      </c>
       <c r="Q223" t="n">
         <v>0</v>
       </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U223" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -33147,7 +31993,7 @@
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
@@ -33157,12 +32003,7 @@
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ223" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr">
@@ -33172,11 +32013,6 @@
       </c>
       <c r="AT223" t="n">
         <v>1</v>
-      </c>
-      <c r="AU223" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
@@ -33287,17 +32123,15 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
+      <c r="P224" t="n">
+        <v>0</v>
+      </c>
       <c r="Q224" t="n">
         <v>0</v>
       </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U224" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -33305,7 +32139,7 @@
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
@@ -33315,12 +32149,7 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ224" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr">
@@ -33330,11 +32159,6 @@
       </c>
       <c r="AT224" t="n">
         <v>1</v>
-      </c>
-      <c r="AU224" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
@@ -33579,17 +32403,15 @@
       <c r="O226" t="n">
         <v>0</v>
       </c>
+      <c r="P226" t="n">
+        <v>0</v>
+      </c>
       <c r="Q226" t="n">
         <v>0</v>
       </c>
       <c r="R226" t="n">
         <v>0</v>
       </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U226" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -33597,7 +32419,7 @@
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
@@ -33607,12 +32429,7 @@
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ226" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr">
@@ -33622,11 +32439,6 @@
       </c>
       <c r="AT226" t="n">
         <v>1</v>
-      </c>
-      <c r="AU226" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
@@ -33868,17 +32680,15 @@
       <c r="O228" t="n">
         <v>0</v>
       </c>
+      <c r="P228" t="n">
+        <v>0</v>
+      </c>
       <c r="Q228" t="n">
         <v>0</v>
       </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U228" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -33886,7 +32696,7 @@
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
@@ -33896,12 +32706,7 @@
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ228" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr">
@@ -33911,11 +32716,6 @@
       </c>
       <c r="AT228" t="n">
         <v>1</v>
-      </c>
-      <c r="AU228" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
@@ -34026,17 +32826,15 @@
       <c r="O229" t="n">
         <v>0</v>
       </c>
+      <c r="P229" t="n">
+        <v>0</v>
+      </c>
       <c r="Q229" t="n">
         <v>0</v>
       </c>
       <c r="R229" t="n">
         <v>0</v>
       </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U229" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -34044,7 +32842,7 @@
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
@@ -34054,12 +32852,7 @@
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ229" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr">
@@ -34069,11 +32862,6 @@
       </c>
       <c r="AT229" t="n">
         <v>1</v>
-      </c>
-      <c r="AU229" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
@@ -34184,17 +32972,15 @@
       <c r="O230" t="n">
         <v>0</v>
       </c>
+      <c r="P230" t="n">
+        <v>0</v>
+      </c>
       <c r="Q230" t="n">
         <v>0</v>
       </c>
       <c r="R230" t="n">
         <v>0</v>
       </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U230" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -34202,7 +32988,7 @@
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
@@ -34212,12 +32998,7 @@
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ230" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr">
@@ -34227,11 +33008,6 @@
       </c>
       <c r="AT230" t="n">
         <v>1</v>
-      </c>
-      <c r="AU230" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
@@ -34342,17 +33118,15 @@
       <c r="O231" t="n">
         <v>0</v>
       </c>
+      <c r="P231" t="n">
+        <v>0</v>
+      </c>
       <c r="Q231" t="n">
         <v>0</v>
       </c>
       <c r="R231" t="n">
         <v>0</v>
       </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U231" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -34360,7 +33134,7 @@
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
@@ -34370,12 +33144,7 @@
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ231" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr">
@@ -34385,11 +33154,6 @@
       </c>
       <c r="AT231" t="n">
         <v>1</v>
-      </c>
-      <c r="AU231" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
@@ -34765,17 +33529,15 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
+      <c r="P234" t="n">
+        <v>0</v>
+      </c>
       <c r="Q234" t="n">
         <v>0</v>
       </c>
       <c r="R234" t="n">
         <v>0</v>
       </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U234" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -34783,7 +33545,7 @@
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO234" t="inlineStr">
@@ -34793,12 +33555,7 @@
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ234" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS234" t="inlineStr">
@@ -34808,11 +33565,6 @@
       </c>
       <c r="AT234" t="n">
         <v>1</v>
-      </c>
-      <c r="AU234" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
@@ -34923,17 +33675,15 @@
       <c r="O235" t="n">
         <v>0</v>
       </c>
+      <c r="P235" t="n">
+        <v>0</v>
+      </c>
       <c r="Q235" t="n">
         <v>0</v>
       </c>
       <c r="R235" t="n">
         <v>0</v>
       </c>
-      <c r="S235" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U235" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -34941,7 +33691,7 @@
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
@@ -34951,12 +33701,7 @@
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ235" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS235" t="inlineStr">
@@ -34966,11 +33711,6 @@
       </c>
       <c r="AT235" t="n">
         <v>1</v>
-      </c>
-      <c r="AU235" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
@@ -35081,17 +33821,15 @@
       <c r="O236" t="n">
         <v>0</v>
       </c>
+      <c r="P236" t="n">
+        <v>0</v>
+      </c>
       <c r="Q236" t="n">
         <v>0</v>
       </c>
       <c r="R236" t="n">
         <v>0</v>
       </c>
-      <c r="S236" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U236" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -35099,7 +33837,7 @@
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">
@@ -35109,12 +33847,7 @@
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ236" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS236" t="inlineStr">
@@ -35124,11 +33857,6 @@
       </c>
       <c r="AT236" t="n">
         <v>1</v>
-      </c>
-      <c r="AU236" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
@@ -35239,17 +33967,15 @@
       <c r="O237" t="n">
         <v>0</v>
       </c>
+      <c r="P237" t="n">
+        <v>0</v>
+      </c>
       <c r="Q237" t="n">
         <v>0</v>
       </c>
       <c r="R237" t="n">
         <v>0</v>
       </c>
-      <c r="S237" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U237" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -35257,7 +33983,7 @@
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">
@@ -35267,12 +33993,7 @@
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ237" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr">
@@ -35282,11 +34003,6 @@
       </c>
       <c r="AT237" t="n">
         <v>1</v>
-      </c>
-      <c r="AU237" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
@@ -35662,17 +34378,15 @@
       <c r="O240" t="n">
         <v>0</v>
       </c>
+      <c r="P240" t="n">
+        <v>0</v>
+      </c>
       <c r="Q240" t="n">
         <v>0</v>
       </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
-      <c r="S240" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U240" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -35680,7 +34394,7 @@
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO240" t="inlineStr">
@@ -35690,12 +34404,7 @@
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ240" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS240" t="inlineStr">
@@ -35705,11 +34414,6 @@
       </c>
       <c r="AT240" t="n">
         <v>1</v>
-      </c>
-      <c r="AU240" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
@@ -35820,17 +34524,15 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
+      <c r="P241" t="n">
+        <v>0</v>
+      </c>
       <c r="Q241" t="n">
         <v>0</v>
       </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
-      <c r="S241" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U241" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -35838,7 +34540,7 @@
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO241" t="inlineStr">
@@ -35848,12 +34550,7 @@
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ241" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS241" t="inlineStr">
@@ -35863,11 +34560,6 @@
       </c>
       <c r="AT241" t="n">
         <v>1</v>
-      </c>
-      <c r="AU241" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
@@ -35978,17 +34670,15 @@
       <c r="O242" t="n">
         <v>0</v>
       </c>
+      <c r="P242" t="n">
+        <v>0</v>
+      </c>
       <c r="Q242" t="n">
         <v>0</v>
       </c>
       <c r="R242" t="n">
         <v>0</v>
       </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U242" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -35996,7 +34686,7 @@
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO242" t="inlineStr">
@@ -36006,12 +34696,7 @@
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ242" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS242" t="inlineStr">
@@ -36021,11 +34706,6 @@
       </c>
       <c r="AT242" t="n">
         <v>1</v>
-      </c>
-      <c r="AU242" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
@@ -36136,17 +34816,15 @@
       <c r="O243" t="n">
         <v>0</v>
       </c>
+      <c r="P243" t="n">
+        <v>0</v>
+      </c>
       <c r="Q243" t="n">
         <v>0</v>
       </c>
       <c r="R243" t="n">
         <v>0</v>
       </c>
-      <c r="S243" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U243" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -36154,7 +34832,7 @@
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO243" t="inlineStr">
@@ -36164,12 +34842,7 @@
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ243" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS243" t="inlineStr">
@@ -36179,11 +34852,6 @@
       </c>
       <c r="AT243" t="n">
         <v>1</v>
-      </c>
-      <c r="AU243" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
@@ -36294,17 +34962,15 @@
       <c r="O244" t="n">
         <v>0</v>
       </c>
+      <c r="P244" t="n">
+        <v>0</v>
+      </c>
       <c r="Q244" t="n">
         <v>0</v>
       </c>
       <c r="R244" t="n">
         <v>0</v>
       </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U244" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -36312,7 +34978,7 @@
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO244" t="inlineStr">
@@ -36322,12 +34988,7 @@
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ244" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS244" t="inlineStr">
@@ -36337,11 +34998,6 @@
       </c>
       <c r="AT244" t="n">
         <v>1</v>
-      </c>
-      <c r="AU244" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
@@ -36717,17 +35373,15 @@
       <c r="O247" t="n">
         <v>0</v>
       </c>
+      <c r="P247" t="n">
+        <v>0</v>
+      </c>
       <c r="Q247" t="n">
         <v>0</v>
       </c>
       <c r="R247" t="n">
         <v>0</v>
       </c>
-      <c r="S247" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U247" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -36735,7 +35389,7 @@
       </c>
       <c r="AA247" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO247" t="inlineStr">
@@ -36745,12 +35399,7 @@
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ247" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS247" t="inlineStr">
@@ -36760,11 +35409,6 @@
       </c>
       <c r="AT247" t="n">
         <v>1</v>
-      </c>
-      <c r="AU247" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
@@ -36875,17 +35519,15 @@
       <c r="O248" t="n">
         <v>0</v>
       </c>
+      <c r="P248" t="n">
+        <v>0</v>
+      </c>
       <c r="Q248" t="n">
         <v>0</v>
       </c>
       <c r="R248" t="n">
         <v>0</v>
       </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U248" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -36893,7 +35535,7 @@
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO248" t="inlineStr">
@@ -36903,12 +35545,7 @@
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ248" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS248" t="inlineStr">
@@ -36918,11 +35555,6 @@
       </c>
       <c r="AT248" t="n">
         <v>1</v>
-      </c>
-      <c r="AU248" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
@@ -37033,17 +35665,15 @@
       <c r="O249" t="n">
         <v>0</v>
       </c>
+      <c r="P249" t="n">
+        <v>0</v>
+      </c>
       <c r="Q249" t="n">
         <v>0</v>
       </c>
       <c r="R249" t="n">
         <v>0</v>
       </c>
-      <c r="S249" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U249" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -37051,7 +35681,7 @@
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO249" t="inlineStr">
@@ -37061,12 +35691,7 @@
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ249" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS249" t="inlineStr">
@@ -37076,11 +35701,6 @@
       </c>
       <c r="AT249" t="n">
         <v>1</v>
-      </c>
-      <c r="AU249" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
@@ -37191,17 +35811,15 @@
       <c r="O250" t="n">
         <v>0</v>
       </c>
+      <c r="P250" t="n">
+        <v>0</v>
+      </c>
       <c r="Q250" t="n">
         <v>0</v>
       </c>
       <c r="R250" t="n">
         <v>0</v>
       </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U250" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -37209,7 +35827,7 @@
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO250" t="inlineStr">
@@ -37219,12 +35837,7 @@
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ250" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS250" t="inlineStr">
@@ -37234,11 +35847,6 @@
       </c>
       <c r="AT250" t="n">
         <v>1</v>
-      </c>
-      <c r="AU250" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
@@ -37614,17 +36222,15 @@
       <c r="O253" t="n">
         <v>0</v>
       </c>
+      <c r="P253" t="n">
+        <v>0</v>
+      </c>
       <c r="Q253" t="n">
         <v>0</v>
       </c>
       <c r="R253" t="n">
         <v>0</v>
       </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U253" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -37632,7 +36238,7 @@
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO253" t="inlineStr">
@@ -37642,12 +36248,7 @@
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ253" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS253" t="inlineStr">
@@ -37657,11 +36258,6 @@
       </c>
       <c r="AT253" t="n">
         <v>1</v>
-      </c>
-      <c r="AU253" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
@@ -37772,17 +36368,15 @@
       <c r="O254" t="n">
         <v>0</v>
       </c>
+      <c r="P254" t="n">
+        <v>0</v>
+      </c>
       <c r="Q254" t="n">
         <v>0</v>
       </c>
       <c r="R254" t="n">
         <v>0</v>
       </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U254" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -37790,7 +36384,7 @@
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO254" t="inlineStr">
@@ -37800,12 +36394,7 @@
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ254" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS254" t="inlineStr">
@@ -37815,11 +36404,6 @@
       </c>
       <c r="AT254" t="n">
         <v>1</v>
-      </c>
-      <c r="AU254" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
@@ -37930,17 +36514,15 @@
       <c r="O255" t="n">
         <v>0</v>
       </c>
+      <c r="P255" t="n">
+        <v>0</v>
+      </c>
       <c r="Q255" t="n">
         <v>0</v>
       </c>
       <c r="R255" t="n">
         <v>0</v>
       </c>
-      <c r="S255" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U255" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -37948,7 +36530,7 @@
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO255" t="inlineStr">
@@ -37958,12 +36540,7 @@
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ255" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS255" t="inlineStr">
@@ -37973,11 +36550,6 @@
       </c>
       <c r="AT255" t="n">
         <v>1</v>
-      </c>
-      <c r="AU255" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
@@ -38088,17 +36660,15 @@
       <c r="O256" t="n">
         <v>0</v>
       </c>
+      <c r="P256" t="n">
+        <v>0</v>
+      </c>
       <c r="Q256" t="n">
         <v>0</v>
       </c>
       <c r="R256" t="n">
         <v>0</v>
       </c>
-      <c r="S256" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U256" t="inlineStr">
         <is>
           <t>HOLD_JP_d38d722b1e545df114640333e053</t>
@@ -38106,7 +36676,7 @@
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO256" t="inlineStr">
@@ -38116,12 +36686,7 @@
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ256" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS256" t="inlineStr">
@@ -38131,11 +36696,6 @@
       </c>
       <c r="AT256" t="n">
         <v>1</v>
-      </c>
-      <c r="AU256" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>

--- a/diseases/d064/2010-2014.xlsx
+++ b/diseases/d064/2010-2014.xlsx
@@ -1152,6 +1152,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1164,12 +1169,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1668,6 +1683,11 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1680,12 +1700,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1802,6 +1832,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1814,12 +1849,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1933,6 +1978,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1945,12 +1995,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2067,6 +2127,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2079,12 +2144,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2198,6 +2273,11 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2210,12 +2290,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2332,6 +2422,11 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2344,12 +2439,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2463,6 +2568,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2475,12 +2585,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2597,6 +2717,11 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2609,12 +2734,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2728,6 +2863,11 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2740,12 +2880,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2862,6 +3012,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2874,12 +3029,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2993,6 +3158,11 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3005,12 +3175,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3127,6 +3307,11 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3139,12 +3324,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3258,6 +3453,11 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3270,12 +3470,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3392,6 +3602,11 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3404,12 +3619,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3523,6 +3748,11 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3535,12 +3765,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3657,6 +3897,11 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3669,12 +3914,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3788,6 +4043,11 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3800,12 +4060,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3922,6 +4192,11 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3934,12 +4209,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4053,6 +4338,11 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4065,12 +4355,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4187,6 +4487,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4199,12 +4504,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4318,6 +4633,11 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4330,12 +4650,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4452,6 +4782,11 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4464,12 +4799,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4583,6 +4928,11 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4595,12 +4945,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5102,6 +5462,11 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5114,12 +5479,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5618,6 +5993,11 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5630,12 +6010,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5752,6 +6142,11 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5764,12 +6159,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5883,6 +6288,11 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5895,12 +6305,22 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6017,6 +6437,11 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6029,12 +6454,22 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6148,6 +6583,11 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6160,12 +6600,22 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6282,6 +6732,11 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6294,12 +6749,22 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6413,6 +6878,11 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6425,12 +6895,22 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6547,6 +7027,11 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6559,12 +7044,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6678,6 +7173,11 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6690,12 +7190,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -6812,6 +7322,11 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6824,12 +7339,22 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -6943,6 +7468,11 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6955,12 +7485,22 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7077,6 +7617,11 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7089,12 +7634,22 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7208,6 +7763,11 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7220,12 +7780,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7342,6 +7912,11 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7354,12 +7929,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7473,6 +8058,11 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7485,12 +8075,22 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7607,6 +8207,11 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7619,12 +8224,22 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -7738,6 +8353,11 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7750,12 +8370,22 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -7872,6 +8502,11 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7884,12 +8519,22 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8003,6 +8648,11 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8015,12 +8665,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8137,6 +8797,11 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8149,12 +8814,22 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8268,6 +8943,11 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8280,12 +8960,22 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8402,6 +9092,11 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8414,12 +9109,22 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8533,6 +9238,11 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8545,12 +9255,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9052,6 +9772,11 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9064,12 +9789,22 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9568,6 +10303,11 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9580,12 +10320,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9702,6 +10452,11 @@
       <c r="R64" t="n">
         <v>0</v>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9714,12 +10469,22 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -9833,6 +10598,11 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9845,12 +10615,22 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -9967,6 +10747,11 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9979,12 +10764,22 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10098,6 +10893,11 @@
       <c r="R67" t="n">
         <v>0</v>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10110,12 +10910,22 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10232,6 +11042,11 @@
       <c r="R68" t="n">
         <v>0</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10244,12 +11059,22 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10363,6 +11188,11 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10375,12 +11205,22 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10497,6 +11337,11 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10509,12 +11354,22 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -10628,6 +11483,11 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10640,12 +11500,22 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -10762,6 +11632,11 @@
       <c r="R72" t="n">
         <v>0</v>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10774,12 +11649,22 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -10893,6 +11778,11 @@
       <c r="R73" t="n">
         <v>0</v>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10905,12 +11795,22 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11027,6 +11927,11 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11039,12 +11944,22 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11158,6 +12073,11 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11170,12 +12090,22 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -11292,6 +12222,11 @@
       <c r="R76" t="n">
         <v>0</v>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11304,12 +12239,22 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -11423,6 +12368,11 @@
       <c r="R77" t="n">
         <v>0</v>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11435,12 +12385,22 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -11557,6 +12517,11 @@
       <c r="R78" t="n">
         <v>0</v>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11569,12 +12534,22 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -11688,6 +12663,11 @@
       <c r="R79" t="n">
         <v>0</v>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11700,12 +12680,22 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12260,6 +13250,11 @@
       <c r="R83" t="n">
         <v>0</v>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12272,12 +13267,22 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -12391,6 +13396,11 @@
       <c r="R84" t="n">
         <v>0</v>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12403,12 +13413,22 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -13109,6 +14129,11 @@
       <c r="R89" t="n">
         <v>0</v>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13121,12 +14146,22 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -13240,6 +14275,11 @@
       <c r="R90" t="n">
         <v>0</v>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13252,12 +14292,22 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -14104,6 +15154,11 @@
       <c r="R96" t="n">
         <v>0</v>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14116,12 +15171,22 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -14235,6 +15300,11 @@
       <c r="R97" t="n">
         <v>0</v>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14247,12 +15317,22 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -15338,6 +16418,11 @@
       <c r="R104" t="n">
         <v>0</v>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15350,12 +16435,22 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -15854,6 +16949,11 @@
       <c r="R107" t="n">
         <v>0</v>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15866,12 +16966,22 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -16572,6 +17682,11 @@
       <c r="R112" t="n">
         <v>0</v>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16584,12 +17699,22 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -16849,6 +17974,11 @@
       <c r="R114" t="n">
         <v>0</v>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16861,12 +17991,22 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
         <v>0</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -17421,6 +18561,11 @@
       <c r="R118" t="n">
         <v>0</v>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17433,12 +18578,22 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -17698,6 +18853,11 @@
       <c r="R120" t="n">
         <v>0</v>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17710,12 +18870,22 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -18416,6 +19586,11 @@
       <c r="R125" t="n">
         <v>0</v>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18428,12 +19603,22 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -18547,6 +19732,11 @@
       <c r="R126" t="n">
         <v>0</v>
       </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18559,12 +19749,22 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -19265,6 +20465,11 @@
       <c r="R131" t="n">
         <v>0</v>
       </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19277,12 +20482,22 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
         <v>0</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -19396,6 +20611,11 @@
       <c r="R132" t="n">
         <v>0</v>
       </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19408,12 +20628,22 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
         <v>0</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -20260,6 +21490,11 @@
       <c r="R138" t="n">
         <v>0</v>
       </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20272,12 +21507,22 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
         <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -20391,6 +21636,11 @@
       <c r="R139" t="n">
         <v>0</v>
       </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20403,12 +21653,22 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -21109,6 +22369,11 @@
       <c r="R144" t="n">
         <v>0</v>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21121,12 +22386,22 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -21240,6 +22515,11 @@
       <c r="R145" t="n">
         <v>0</v>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21252,12 +22532,22 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -21958,6 +23248,11 @@
       <c r="R150" t="n">
         <v>0</v>
       </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21970,12 +23265,22 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
         <v>0</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -22089,6 +23394,11 @@
       <c r="R151" t="n">
         <v>0</v>
       </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22101,12 +23411,22 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
         <v>0</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -22953,6 +24273,11 @@
       <c r="R157" t="n">
         <v>0</v>
       </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22965,12 +24290,22 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
         <v>0</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -23084,6 +24419,11 @@
       <c r="R158" t="n">
         <v>0</v>
       </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23096,12 +24436,22 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
         <v>0</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -23802,6 +25152,11 @@
       <c r="R163" t="n">
         <v>0</v>
       </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23814,12 +25169,22 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
         <v>0</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
@@ -23933,6 +25298,11 @@
       <c r="R164" t="n">
         <v>0</v>
       </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23945,12 +25315,22 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
         <v>0</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -24651,6 +26031,11 @@
       <c r="R169" t="n">
         <v>0</v>
       </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24663,12 +26048,22 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
         <v>0</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -24928,6 +26323,11 @@
       <c r="R171" t="n">
         <v>0</v>
       </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24940,12 +26340,22 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
         <v>0</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -25646,6 +27056,11 @@
       <c r="R176" t="n">
         <v>0</v>
       </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25658,12 +27073,22 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr"/>
       <c r="AT176" t="n">
         <v>0</v>
+      </c>
+      <c r="AU176" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
@@ -25777,6 +27202,11 @@
       <c r="R177" t="n">
         <v>0</v>
       </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25789,12 +27219,22 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
         <v>0</v>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
@@ -26880,6 +28320,11 @@
       <c r="R184" t="n">
         <v>0</v>
       </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26892,12 +28337,22 @@
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr"/>
       <c r="AT184" t="n">
         <v>0</v>
+      </c>
+      <c r="AU184" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
@@ -27396,6 +28851,11 @@
       <c r="R187" t="n">
         <v>0</v>
       </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27408,12 +28868,22 @@
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="n">
         <v>0</v>
+      </c>
+      <c r="AU187" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
@@ -28260,6 +29730,11 @@
       <c r="R193" t="n">
         <v>0</v>
       </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28272,12 +29747,22 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
         <v>0</v>
+      </c>
+      <c r="AU193" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
@@ -28391,6 +29876,11 @@
       <c r="R194" t="n">
         <v>0</v>
       </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28403,12 +29893,22 @@
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS194" t="inlineStr"/>
       <c r="AT194" t="n">
         <v>0</v>
+      </c>
+      <c r="AU194" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
@@ -29109,6 +30609,11 @@
       <c r="R199" t="n">
         <v>0</v>
       </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29121,12 +30626,22 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
         <v>0</v>
+      </c>
+      <c r="AU199" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
@@ -29240,6 +30755,11 @@
       <c r="R200" t="n">
         <v>0</v>
       </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29252,12 +30772,22 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
         <v>0</v>
+      </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
@@ -29958,6 +31488,11 @@
       <c r="R205" t="n">
         <v>0</v>
       </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29970,12 +31505,22 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
         <v>0</v>
+      </c>
+      <c r="AU205" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
@@ -30089,6 +31634,11 @@
       <c r="R206" t="n">
         <v>0</v>
       </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30101,12 +31651,22 @@
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS206" t="inlineStr"/>
       <c r="AT206" t="n">
         <v>0</v>
+      </c>
+      <c r="AU206" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
@@ -30807,6 +32367,11 @@
       <c r="R211" t="n">
         <v>0</v>
       </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30819,12 +32384,22 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr"/>
       <c r="AT211" t="n">
         <v>0</v>
+      </c>
+      <c r="AU211" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
@@ -30938,6 +32513,11 @@
       <c r="R212" t="n">
         <v>0</v>
       </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30950,12 +32530,22 @@
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr"/>
       <c r="AT212" t="n">
         <v>0</v>
+      </c>
+      <c r="AU212" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
@@ -31802,6 +33392,11 @@
       <c r="R218" t="n">
         <v>0</v>
       </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA218" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31814,12 +33409,22 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr"/>
       <c r="AT218" t="n">
         <v>0</v>
+      </c>
+      <c r="AU218" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
@@ -31933,6 +33538,11 @@
       <c r="R219" t="n">
         <v>0</v>
       </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA219" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31945,12 +33555,22 @@
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS219" t="inlineStr"/>
       <c r="AT219" t="n">
         <v>0</v>
+      </c>
+      <c r="AU219" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
@@ -32651,6 +34271,11 @@
       <c r="R224" t="n">
         <v>0</v>
       </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32663,12 +34288,22 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr"/>
       <c r="AT224" t="n">
         <v>0</v>
+      </c>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
@@ -32782,6 +34417,11 @@
       <c r="R225" t="n">
         <v>0</v>
       </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA225" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32794,12 +34434,22 @@
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR225" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr"/>
       <c r="AT225" t="n">
         <v>0</v>
+      </c>
+      <c r="AU225" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
@@ -33500,6 +35150,11 @@
       <c r="R230" t="n">
         <v>0</v>
       </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33512,12 +35167,22 @@
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr"/>
       <c r="AT230" t="n">
         <v>0</v>
+      </c>
+      <c r="AU230" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
@@ -33777,6 +35442,11 @@
       <c r="R232" t="n">
         <v>0</v>
       </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33789,12 +35459,22 @@
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS232" t="inlineStr"/>
       <c r="AT232" t="n">
         <v>0</v>
+      </c>
+      <c r="AU232" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
@@ -34495,6 +36175,11 @@
       <c r="R237" t="n">
         <v>0</v>
       </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA237" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34507,12 +36192,22 @@
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR237" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr"/>
       <c r="AT237" t="n">
         <v>0</v>
+      </c>
+      <c r="AU237" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
@@ -34626,6 +36321,11 @@
       <c r="R238" t="n">
         <v>0</v>
       </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34638,12 +36338,22 @@
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR238" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr"/>
       <c r="AT238" t="n">
         <v>0</v>
+      </c>
+      <c r="AU238" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
@@ -35344,6 +37054,11 @@
       <c r="R243" t="n">
         <v>0</v>
       </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35356,12 +37071,22 @@
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR243" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS243" t="inlineStr"/>
       <c r="AT243" t="n">
         <v>0</v>
+      </c>
+      <c r="AU243" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
@@ -35475,6 +37200,11 @@
       <c r="R244" t="n">
         <v>0</v>
       </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA244" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35487,12 +37217,22 @@
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR244" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS244" t="inlineStr"/>
       <c r="AT244" t="n">
         <v>0</v>
+      </c>
+      <c r="AU244" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
@@ -36339,6 +38079,11 @@
       <c r="R250" t="n">
         <v>0</v>
       </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA250" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36351,12 +38096,22 @@
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR250" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS250" t="inlineStr"/>
       <c r="AT250" t="n">
         <v>0</v>
+      </c>
+      <c r="AU250" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
@@ -36470,6 +38225,11 @@
       <c r="R251" t="n">
         <v>0</v>
       </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36482,12 +38242,22 @@
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS251" t="inlineStr"/>
       <c r="AT251" t="n">
         <v>0</v>
+      </c>
+      <c r="AU251" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
@@ -37188,6 +38958,11 @@
       <c r="R256" t="n">
         <v>0</v>
       </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA256" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37200,12 +38975,22 @@
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS256" t="inlineStr"/>
       <c r="AT256" t="n">
         <v>0</v>
+      </c>
+      <c r="AU256" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
@@ -37319,6 +39104,11 @@
       <c r="R257" t="n">
         <v>0</v>
       </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37331,12 +39121,22 @@
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR257" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS257" t="inlineStr"/>
       <c r="AT257" t="n">
         <v>0</v>
+      </c>
+      <c r="AU257" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
